--- a/generated/spreadsheet/reserved-matters-reserved-matters.xlsx
+++ b/generated/spreadsheet/reserved-matters-reserved-matters.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
@@ -808,7 +808,7 @@
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Planning requirement references identifying the information this document provides. A document may address more than one requirement. These references identify its coverage; they do not establish that the requirements have been satisfied.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Planning officer name</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Reserved matters[]</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -2351,12 +2351,12 @@
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Identifies which reserved matters are being submitted for approval as part of this application</t>
+          <t>A description of the development, works, change of use or reserved matters for which approval is sought</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2370,24 +2370,20 @@
       <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Related application</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Reserved matters[]</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>Identifies which reserved matters are being submitted for approval as part of this application</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -2406,14 +2402,14 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>A description of the related application</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2437,63 +2433,55 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Decision date</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>A description of the related application</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related application</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>A polygon or multipolygon boundary</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>multipolygon</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2502,28 +2490,24 @@
       <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related application</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Site address</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>EIA application</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Text representation of an address or site</t>
+          <t>Whether the related application was an Environmental Impact Assessment application</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2537,28 +2521,24 @@
       <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related application</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Site address</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Environmental statement submitted</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Postcode for a contact address or site</t>
+          <t>Whether an Environmental Statement was submitted with the related application</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2572,33 +2552,25 @@
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Site address</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Proposal started</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2607,28 +2579,20 @@
       <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Site address</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>USRNs[]</t>
-        </is>
-      </c>
+          <t>Proposal start date</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -2642,29 +2606,25 @@
       <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Easting</t>
-        </is>
-      </c>
+          <t>Proposal completed</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2673,24 +2633,20 @@
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Northing</t>
-        </is>
-      </c>
+          <t>Proposal completion date</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -2700,8 +2656,16 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="2" t="n"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -2709,24 +2673,24 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2740,59 +2704,63 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr"/>
-      <c r="E69" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2801,25 +2769,33 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2828,15 +2804,23 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr"/>
-      <c r="E71" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -2855,29 +2839,29 @@
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2886,29 +2870,29 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2917,94 +2901,90 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Supporting information</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Any additional information which will help with the planning application</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Replacement drawings[]</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Old drawing reference</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Reference of the old drawing being replaced</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n"/>
-      <c r="B76" s="2" t="n"/>
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Replacement drawings[]</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>New drawing reference</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Reference for the new drawing that replaces the old drawing</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -3018,27 +2998,329 @@
       <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Replacement drawings[]</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>A textual reason</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n"/>
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>The complete name of a person</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n"/>
+      <c r="B80" s="2" t="n"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n"/>
+      <c r="B81" s="2" t="n"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Supporting information</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Drawings approved as part of the original decision and drawings submitted with the reserved matters application</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Approved drawings[]</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Name or title of the approved drawing</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Approved drawings[]</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Reference number of the approved drawing</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n"/>
+      <c r="B84" s="2" t="n"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Submitted drawing references[]</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Reference numbers of drawings submitted with the application for approval</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Approved drawings schedule</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>A unique reference for the data item</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Submitted drawings schedule</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>A unique reference for the data item</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n"/>
+      <c r="B87" s="2" t="n"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Reasons for any changes to the original drawings</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -3046,32 +3328,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B56:B59"/>
+    <mergeCell ref="B67:B75"/>
     <mergeCell ref="A37:A43"/>
     <mergeCell ref="A2:A19"/>
+    <mergeCell ref="A82:A87"/>
     <mergeCell ref="A44"/>
     <mergeCell ref="B37:B43"/>
     <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B60:B68"/>
-    <mergeCell ref="A69:A74"/>
+    <mergeCell ref="A56:A66"/>
     <mergeCell ref="B51:B55"/>
-    <mergeCell ref="A56:A59"/>
+    <mergeCell ref="B82:B87"/>
     <mergeCell ref="B24:B32"/>
     <mergeCell ref="A33:A36"/>
     <mergeCell ref="A45:A47"/>
-    <mergeCell ref="B75:B77"/>
     <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B69:B74"/>
     <mergeCell ref="A51:A55"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="B33:B36"/>
-    <mergeCell ref="A75:A77"/>
+    <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A67:A75"/>
     <mergeCell ref="A24:A32"/>
     <mergeCell ref="B44"/>
     <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B56:B66"/>
     <mergeCell ref="B20:B23"/>
-    <mergeCell ref="A60:A68"/>
     <mergeCell ref="B2:B19"/>
+    <mergeCell ref="B76:B81"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
